--- a/SAMSUNG_corrected.xlsx
+++ b/SAMSUNG_corrected.xlsx
@@ -1,180 +1,239 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="11280" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="11880"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+  <si>
+    <t>MODEL</t>
+  </si>
+  <si>
+    <t>STORAGE</t>
+  </si>
+  <si>
+    <t>PRICE</t>
+  </si>
+  <si>
+    <t>RMB</t>
+  </si>
+  <si>
+    <t>XR</t>
+  </si>
+  <si>
+    <t>64GB</t>
+  </si>
+  <si>
+    <t>128GB</t>
+  </si>
+  <si>
+    <t>IPHONE 11</t>
+  </si>
+  <si>
+    <t>IPHONE 11 PRO</t>
+  </si>
+  <si>
+    <t>256GB</t>
+  </si>
+  <si>
+    <t>IPHONE 11 PRO MAX</t>
+  </si>
+  <si>
+    <t>IPHONE 12</t>
+  </si>
+  <si>
+    <t>IPHONE 12 PRO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -474,159 +533,156 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -874,7 +930,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -883,7 +939,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -896,74 +952,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1215,210 +1208,169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MODEL</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>STORAGE</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>PRICE</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>XR</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>64GB</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
         <v>170000</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>690</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>128GB</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
+    <row r="3" spans="1:4">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
         <v>182000</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>747</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>IPHONE 11</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>64GB</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
         <v>209000</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>876</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>128GB</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
+    <row r="5" spans="1:4">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
         <v>224000</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>947</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>IPHONE 11 PRO</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>64GB</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6">
         <v>256000</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>1100</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>256GB</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
+    <row r="7" spans="1:4">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
         <v>277000</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>1200</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>IPHONE 11 PRO MAX</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>64GB</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8">
         <v>277000</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>1200</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>256GB</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
+    <row r="9" spans="1:4">
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
         <v>298000</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>1300</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>IPHONE 12</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>64GB</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10">
         <v>224000</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>947</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>128GB</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
+    <row r="11" spans="1:4">
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11">
         <v>245000</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>1047</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>IPHONE 12 PRO</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>128GB</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="n">
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12">
         <v>319000</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>1400</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>